--- a/leaderboard.xlsx
+++ b/leaderboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LEADERBOARD APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E4A0A34-663D-4E77-893B-40712936C967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A59B2B-D405-459F-93AD-C5659444B6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6CFCDAFB-F81F-46DB-AA55-62CB1CA670F5}"/>
   </bookViews>
@@ -489,109 +489,145 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="2"/>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2"/>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="2"/>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="2"/>
+      <c r="B18" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="19" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="2"/>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/leaderboard.xlsx
+++ b/leaderboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LEADERBOARD APP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A59B2B-D405-459F-93AD-C5659444B6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65FD2290-9A6A-462F-B76B-5299DA235292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6CFCDAFB-F81F-46DB-AA55-62CB1CA670F5}"/>
   </bookViews>
@@ -36,12 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
-    <t>NAMA</t>
-  </si>
-  <si>
-    <t>POIN</t>
-  </si>
-  <si>
     <t>MAYA ANDINI</t>
   </si>
   <si>
@@ -94,6 +88,12 @@
   </si>
   <si>
     <t>DIKA IBNU KAMAL</t>
+  </si>
+  <si>
+    <t>Nama</t>
+  </si>
+  <si>
+    <t>Poin</t>
   </si>
 </sst>
 </file>
@@ -479,15 +479,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" s="2">
         <v>0</v>
@@ -495,7 +495,7 @@
     </row>
     <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2">
         <v>0</v>
@@ -503,7 +503,7 @@
     </row>
     <row r="4" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2">
         <v>0</v>
@@ -511,7 +511,7 @@
     </row>
     <row r="5" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5" s="2">
         <v>0</v>
@@ -519,7 +519,7 @@
     </row>
     <row r="6" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2">
         <v>0</v>
@@ -527,7 +527,7 @@
     </row>
     <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2">
         <v>0</v>
@@ -535,7 +535,7 @@
     </row>
     <row r="8" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2">
         <v>0</v>
@@ -543,7 +543,7 @@
     </row>
     <row r="9" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2">
         <v>0</v>
@@ -551,7 +551,7 @@
     </row>
     <row r="10" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2">
         <v>0</v>
@@ -559,7 +559,7 @@
     </row>
     <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2">
         <v>0</v>
@@ -567,7 +567,7 @@
     </row>
     <row r="12" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2">
         <v>0</v>
@@ -575,7 +575,7 @@
     </row>
     <row r="13" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
@@ -583,7 +583,7 @@
     </row>
     <row r="14" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -591,7 +591,7 @@
     </row>
     <row r="15" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2">
         <v>0</v>
@@ -599,7 +599,7 @@
     </row>
     <row r="16" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -607,7 +607,7 @@
     </row>
     <row r="17" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2">
         <v>0</v>
@@ -615,7 +615,7 @@
     </row>
     <row r="18" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2">
         <v>0</v>
@@ -623,7 +623,7 @@
     </row>
     <row r="19" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2">
         <v>0</v>
